--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
@@ -188,7 +188,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -996,7 +998,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5">
         <f>Config!$B$4&amp;" · Carteira de clientes e casos · "&amp;TEXT(DAY(Config!$B$5),"00")&amp;"/"&amp;TEXT(MONTH(Config!$B$5),"00")&amp;"/"&amp;YEAR(Config!$B$5)</f>
         <v/>
@@ -2602,7 +2604,7 @@
     <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Configurações</t>
@@ -2829,8 +2831,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -2863,7 +2866,7 @@
     <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Clientes</t>
@@ -5368,7 +5371,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:J64"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H64">
@@ -5412,7 +5416,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Casos</t>
@@ -12043,8 +12047,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:M204"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <conditionalFormatting sqref="I5:I204">
     <cfRule type="expression" priority="1" dxfId="1">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie a tabela "Por área" e o "Top 5 clientes" e use o prompt "Resumir a carteira" da biblioteca para preparar a reunião de sócios ou a conversa com o contador.</t>
+          <t>Copie a tabela "Por área" e o "Top 5 clientes" e use o prompt "Clientes 01 · Resumir a carteira para o sócio" da biblioteca para preparar a reunião de sócios ou a conversa com o contador.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Em Casos, uma linha por caso: número do processo (ou uma referência sua, para consultivo), cliente, área, fase, responsável, modalidade, valor contratado, recebido até hoje e data de abertura. Atualize o recebido a cada pagamento.</t>
+          <t>Em Casos, uma linha por caso: número do processo (ou uma referência sua, para consultivo), cliente, área, fase, responsável, modalidade, valor contratado, recebido até hoje e data de abertura. Atualize o recebido a cada pagamento (é a soma das parcelas pagas na planilha 14). Esta aba é a fonte do cadastro: as planilhas 01, 02, 04, 08, 14 e 16 copiam daqui.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -999,9 +999,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Carteira de clientes e casos · "&amp;TEXT(DAY(Config!$B$5),"00")&amp;"/"&amp;TEXT(MONTH(Config!$B$5),"00")&amp;"/"&amp;YEAR(Config!$B$5)</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Carteira de clientes e casos · 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1052,32 +1052,32 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13">
         <f>SUM(Casos!$H$5:$H$204)</f>
-        <v/>
+        <v>383900</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="14">
         <f>SUM(Casos!$I$5:$I$204)</f>
-        <v/>
+        <v>271910</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="15">
         <f>SUM(Casos!$H$5:$H$204)-SUM(Casos!$I$5:$I$204)</f>
-        <v/>
+        <v>111990</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="16">
         <f>IFERROR(C5/A5,0)</f>
-        <v/>
+        <v>0.708283407137275</v>
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="17">
         <f>COUNTIFS(Casos!$L$5:$L$204,"Ativo")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="17">
         <f>COUNTIFS(Casos!$L$5:$L$204,"Encerrado")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="L5" s="8" t="n"/>
     </row>
@@ -1131,173 +1131,173 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20">
+      <c r="A9" s="20" t="str">
         <f>IF(Config!$A$9="","",Config!$A$9)</f>
-        <v/>
+        <v>Cível</v>
       </c>
       <c r="B9" s="21">
         <f>IF(Config!$A$9="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$9))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C9" s="21">
         <f>IF(Config!$A$9="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$9,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D9" s="22">
         <f>IF(Config!$A$9="","",SUMIFS(Casos!$H$5:$H$204,Casos!$D$5:$D$204,Config!$A$9))</f>
-        <v/>
+        <v>101500</v>
       </c>
       <c r="E9" s="22">
         <f>IF(Config!$A$9="","",SUMIFS(Casos!$I$5:$I$204,Casos!$D$5:$D$204,Config!$A$9))</f>
-        <v/>
+        <v>70300</v>
       </c>
       <c r="F9" s="22">
         <f>IF(Config!$A$9="","",D9-E9)</f>
-        <v/>
+        <v>31200</v>
       </c>
       <c r="G9" s="23">
         <f>IF(OR(Config!$A$9="",D9=0),"",E9/D9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="24">
+        <v>0.692610837438424</v>
+      </c>
+      <c r="H9" s="24" t="str">
         <f>IF(Config!$A$9="","",REPT("█",ROUND(IFERROR(D9/MAX($D$9:$D$18),0)*20,0)))</f>
-        <v/>
+        <v>██████████████████</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20">
+      <c r="A10" s="20" t="str">
         <f>IF(Config!$A$10="","",Config!$A$10)</f>
-        <v/>
+        <v>Trabalhista</v>
       </c>
       <c r="B10" s="21">
         <f>IF(Config!$A$10="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$10))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C10" s="21">
         <f>IF(Config!$A$10="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$10,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="D10" s="22">
         <f>IF(Config!$A$10="","",SUMIFS(Casos!$H$5:$H$204,Casos!$D$5:$D$204,Config!$A$10))</f>
-        <v/>
+        <v>105400</v>
       </c>
       <c r="E10" s="22">
         <f>IF(Config!$A$10="","",SUMIFS(Casos!$I$5:$I$204,Casos!$D$5:$D$204,Config!$A$10))</f>
-        <v/>
+        <v>67700</v>
       </c>
       <c r="F10" s="22">
         <f>IF(Config!$A$10="","",D10-E10)</f>
-        <v/>
+        <v>37700</v>
       </c>
       <c r="G10" s="23">
         <f>IF(OR(Config!$A$10="",D10=0),"",E10/D10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="24">
+        <v>0.642314990512334</v>
+      </c>
+      <c r="H10" s="24" t="str">
         <f>IF(Config!$A$10="","",REPT("█",ROUND(IFERROR(D10/MAX($D$9:$D$18),0)*20,0)))</f>
-        <v/>
+        <v>██████████████████</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20">
+      <c r="A11" s="20" t="str">
         <f>IF(Config!$A$11="","",Config!$A$11)</f>
-        <v/>
+        <v>Previdenciário</v>
       </c>
       <c r="B11" s="21">
         <f>IF(Config!$A$11="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$11))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C11" s="21">
         <f>IF(Config!$A$11="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$11,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D11" s="22">
         <f>IF(Config!$A$11="","",SUMIFS(Casos!$H$5:$H$204,Casos!$D$5:$D$204,Config!$A$11))</f>
-        <v/>
+        <v>39400</v>
       </c>
       <c r="E11" s="22">
         <f>IF(Config!$A$11="","",SUMIFS(Casos!$I$5:$I$204,Casos!$D$5:$D$204,Config!$A$11))</f>
-        <v/>
+        <v>27650</v>
       </c>
       <c r="F11" s="22">
         <f>IF(Config!$A$11="","",D11-E11)</f>
-        <v/>
+        <v>11750</v>
       </c>
       <c r="G11" s="23">
         <f>IF(OR(Config!$A$11="",D11=0),"",E11/D11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="24">
+        <v>0.701776649746193</v>
+      </c>
+      <c r="H11" s="24" t="str">
         <f>IF(Config!$A$11="","",REPT("█",ROUND(IFERROR(D11/MAX($D$9:$D$18),0)*20,0)))</f>
-        <v/>
+        <v>███████</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20">
+      <c r="A12" s="20" t="str">
         <f>IF(Config!$A$12="","",Config!$A$12)</f>
-        <v/>
+        <v>Empresarial</v>
       </c>
       <c r="B12" s="21">
         <f>IF(Config!$A$12="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$12))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C12" s="21">
         <f>IF(Config!$A$12="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$12,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D12" s="22">
         <f>IF(Config!$A$12="","",SUMIFS(Casos!$H$5:$H$204,Casos!$D$5:$D$204,Config!$A$12))</f>
-        <v/>
+        <v>115000</v>
       </c>
       <c r="E12" s="22">
         <f>IF(Config!$A$12="","",SUMIFS(Casos!$I$5:$I$204,Casos!$D$5:$D$204,Config!$A$12))</f>
-        <v/>
+        <v>85760</v>
       </c>
       <c r="F12" s="22">
         <f>IF(Config!$A$12="","",D12-E12)</f>
-        <v/>
+        <v>29240</v>
       </c>
       <c r="G12" s="23">
         <f>IF(OR(Config!$A$12="",D12=0),"",E12/D12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="24">
+        <v>0.745739130434783</v>
+      </c>
+      <c r="H12" s="24" t="str">
         <f>IF(Config!$A$12="","",REPT("█",ROUND(IFERROR(D12/MAX($D$9:$D$18),0)*20,0)))</f>
-        <v/>
+        <v>████████████████████</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20">
+      <c r="A13" s="20" t="str">
         <f>IF(Config!$A$13="","",Config!$A$13)</f>
-        <v/>
+        <v>Família</v>
       </c>
       <c r="B13" s="21">
         <f>IF(Config!$A$13="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$13))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C13" s="21">
         <f>IF(Config!$A$13="","",COUNTIFS(Casos!$D$5:$D$204,Config!$A$13,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D13" s="22">
         <f>IF(Config!$A$13="","",SUMIFS(Casos!$H$5:$H$204,Casos!$D$5:$D$204,Config!$A$13))</f>
-        <v/>
+        <v>22600</v>
       </c>
       <c r="E13" s="22">
         <f>IF(Config!$A$13="","",SUMIFS(Casos!$I$5:$I$204,Casos!$D$5:$D$204,Config!$A$13))</f>
-        <v/>
+        <v>20500</v>
       </c>
       <c r="F13" s="22">
         <f>IF(Config!$A$13="","",D13-E13)</f>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="G13" s="23">
         <f>IF(OR(Config!$A$13="",D13=0),"",E13/D13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="24">
+        <v>0.907079646017699</v>
+      </c>
+      <c r="H13" s="24" t="str">
         <f>IF(Config!$A$13="","",REPT("█",ROUND(IFERROR(D13/MAX($D$9:$D$18),0)*20,0)))</f>
-        <v/>
+        <v>████</v>
       </c>
     </row>
     <row r="14">
@@ -1520,97 +1520,97 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20">
+      <c r="A22" s="20" t="str">
         <f>IF(Config!$E$9="","",Config!$E$9)</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
       <c r="B22" s="21">
         <f>IF(Config!$E$9="","",COUNTIFS(Casos!$F$5:$F$204,Config!$E$9))</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="C22" s="21">
         <f>IF(Config!$E$9="","",COUNTIFS(Casos!$F$5:$F$204,Config!$E$9,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="D22" s="22">
         <f>IF(Config!$E$9="","",SUMIFS(Casos!$H$5:$H$204,Casos!$F$5:$F$204,Config!$E$9))</f>
-        <v/>
+        <v>239100</v>
       </c>
       <c r="E22" s="22">
         <f>IF(Config!$E$9="","",SUMIFS(Casos!$I$5:$I$204,Casos!$F$5:$F$204,Config!$E$9))</f>
-        <v/>
+        <v>176560</v>
       </c>
       <c r="F22" s="22">
         <f>IF(Config!$E$9="","",D22-E22)</f>
-        <v/>
+        <v>62540</v>
       </c>
       <c r="G22" s="23">
         <f>IF(OR(Config!$E$9="",D22=0),"",E22/D22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="24">
+        <v>0.738435800920117</v>
+      </c>
+      <c r="H22" s="24" t="str">
         <f>IF(Config!$E$9="","",REPT("█",ROUND(IFERROR(D22/MAX($D$22:$D$31),0)*20,0)))</f>
-        <v/>
+        <v>████████████████████</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20">
+      <c r="A23" s="20" t="str">
         <f>IF(Config!$E$10="","",Config!$E$10)</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
       <c r="B23" s="21">
         <f>IF(Config!$E$10="","",COUNTIFS(Casos!$F$5:$F$204,Config!$E$10))</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="C23" s="21">
         <f>IF(Config!$E$10="","",COUNTIFS(Casos!$F$5:$F$204,Config!$E$10,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="D23" s="22">
         <f>IF(Config!$E$10="","",SUMIFS(Casos!$H$5:$H$204,Casos!$F$5:$F$204,Config!$E$10))</f>
-        <v/>
+        <v>144800</v>
       </c>
       <c r="E23" s="22">
         <f>IF(Config!$E$10="","",SUMIFS(Casos!$I$5:$I$204,Casos!$F$5:$F$204,Config!$E$10))</f>
-        <v/>
+        <v>95350</v>
       </c>
       <c r="F23" s="22">
         <f>IF(Config!$E$10="","",D23-E23)</f>
-        <v/>
+        <v>49450</v>
       </c>
       <c r="G23" s="23">
         <f>IF(OR(Config!$E$10="",D23=0),"",E23/D23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="24">
+        <v>0.658494475138122</v>
+      </c>
+      <c r="H23" s="24" t="str">
         <f>IF(Config!$E$10="","",REPT("█",ROUND(IFERROR(D23/MAX($D$22:$D$31),0)*20,0)))</f>
-        <v/>
+        <v>████████████</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20">
+      <c r="A24" s="20" t="str">
         <f>IF(Config!$E$11="","",Config!$E$11)</f>
-        <v/>
+        <v>Júlia Prado</v>
       </c>
       <c r="B24" s="21">
         <f>IF(Config!$E$11="","",COUNTIFS(Casos!$F$5:$F$204,Config!$E$11))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C24" s="21">
         <f>IF(Config!$E$11="","",COUNTIFS(Casos!$F$5:$F$204,Config!$E$11,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D24" s="22">
         <f>IF(Config!$E$11="","",SUMIFS(Casos!$H$5:$H$204,Casos!$F$5:$F$204,Config!$E$11))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E24" s="22">
         <f>IF(Config!$E$11="","",SUMIFS(Casos!$I$5:$I$204,Casos!$F$5:$F$204,Config!$E$11))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F24" s="22">
         <f>IF(Config!$E$11="","",D24-E24)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G24" s="23">
         <f>IF(OR(Config!$E$11="",D24=0),"",E24/D24)</f>
@@ -1909,139 +1909,139 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20">
+      <c r="A35" s="20" t="str">
         <f>IF(Config!$G$9="","",Config!$G$9)</f>
-        <v/>
+        <v>Fixo</v>
       </c>
       <c r="B35" s="21">
         <f>IF(Config!$G$9="","",COUNTIFS(Casos!$G$5:$G$204,Config!$G$9))</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="C35" s="21">
         <f>IF(Config!$G$9="","",COUNTIFS(Casos!$G$5:$G$204,Config!$G$9,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="D35" s="22">
         <f>IF(Config!$G$9="","",SUMIFS(Casos!$H$5:$H$204,Casos!$G$5:$G$204,Config!$G$9))</f>
-        <v/>
+        <v>209400</v>
       </c>
       <c r="E35" s="22">
         <f>IF(Config!$G$9="","",SUMIFS(Casos!$I$5:$I$204,Casos!$G$5:$G$204,Config!$G$9))</f>
-        <v/>
+        <v>163550</v>
       </c>
       <c r="F35" s="22">
         <f>IF(Config!$G$9="","",D35-E35)</f>
-        <v/>
+        <v>45850</v>
       </c>
       <c r="G35" s="23">
         <f>IF(OR(Config!$G$9="",D35=0),"",E35/D35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="24">
+        <v>0.781041069723018</v>
+      </c>
+      <c r="H35" s="24" t="str">
         <f>IF(Config!$G$9="","",REPT("█",ROUND(IFERROR(D35/MAX($D$35:$D$44),0)*20,0)))</f>
-        <v/>
+        <v>████████████████████</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20">
+      <c r="A36" s="20" t="str">
         <f>IF(Config!$G$10="","",Config!$G$10)</f>
-        <v/>
+        <v>Hora</v>
       </c>
       <c r="B36" s="21">
         <f>IF(Config!$G$10="","",COUNTIFS(Casos!$G$5:$G$204,Config!$G$10))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C36" s="21">
         <f>IF(Config!$G$10="","",COUNTIFS(Casos!$G$5:$G$204,Config!$G$10,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D36" s="22">
         <f>IF(Config!$G$10="","",SUMIFS(Casos!$H$5:$H$204,Casos!$G$5:$G$204,Config!$G$10))</f>
-        <v/>
+        <v>45600</v>
       </c>
       <c r="E36" s="22">
         <f>IF(Config!$G$10="","",SUMIFS(Casos!$I$5:$I$204,Casos!$G$5:$G$204,Config!$G$10))</f>
-        <v/>
+        <v>38160</v>
       </c>
       <c r="F36" s="22">
         <f>IF(Config!$G$10="","",D36-E36)</f>
-        <v/>
+        <v>7440</v>
       </c>
       <c r="G36" s="23">
         <f>IF(OR(Config!$G$10="",D36=0),"",E36/D36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="24">
+        <v>0.836842105263158</v>
+      </c>
+      <c r="H36" s="24" t="str">
         <f>IF(Config!$G$10="","",REPT("█",ROUND(IFERROR(D36/MAX($D$35:$D$44),0)*20,0)))</f>
-        <v/>
+        <v>████</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20">
+      <c r="A37" s="20" t="str">
         <f>IF(Config!$G$11="","",Config!$G$11)</f>
-        <v/>
+        <v>Êxito</v>
       </c>
       <c r="B37" s="21">
         <f>IF(Config!$G$11="","",COUNTIFS(Casos!$G$5:$G$204,Config!$G$11))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C37" s="21">
         <f>IF(Config!$G$11="","",COUNTIFS(Casos!$G$5:$G$204,Config!$G$11,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D37" s="22">
         <f>IF(Config!$G$11="","",SUMIFS(Casos!$H$5:$H$204,Casos!$G$5:$G$204,Config!$G$11))</f>
-        <v/>
+        <v>42500</v>
       </c>
       <c r="E37" s="22">
         <f>IF(Config!$G$11="","",SUMIFS(Casos!$I$5:$I$204,Casos!$G$5:$G$204,Config!$G$11))</f>
-        <v/>
+        <v>12500</v>
       </c>
       <c r="F37" s="22">
         <f>IF(Config!$G$11="","",D37-E37)</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="G37" s="23">
         <f>IF(OR(Config!$G$11="",D37=0),"",E37/D37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="24">
+        <v>0.294117647058824</v>
+      </c>
+      <c r="H37" s="24" t="str">
         <f>IF(Config!$G$11="","",REPT("█",ROUND(IFERROR(D37/MAX($D$35:$D$44),0)*20,0)))</f>
-        <v/>
+        <v>████</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20">
+      <c r="A38" s="20" t="str">
         <f>IF(Config!$G$12="","",Config!$G$12)</f>
-        <v/>
+        <v>Misto</v>
       </c>
       <c r="B38" s="21">
         <f>IF(Config!$G$12="","",COUNTIFS(Casos!$G$5:$G$204,Config!$G$12))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C38" s="21">
         <f>IF(Config!$G$12="","",COUNTIFS(Casos!$G$5:$G$204,Config!$G$12,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D38" s="22">
         <f>IF(Config!$G$12="","",SUMIFS(Casos!$H$5:$H$204,Casos!$G$5:$G$204,Config!$G$12))</f>
-        <v/>
+        <v>86400</v>
       </c>
       <c r="E38" s="22">
         <f>IF(Config!$G$12="","",SUMIFS(Casos!$I$5:$I$204,Casos!$G$5:$G$204,Config!$G$12))</f>
-        <v/>
+        <v>57700</v>
       </c>
       <c r="F38" s="22">
         <f>IF(Config!$G$12="","",D38-E38)</f>
-        <v/>
+        <v>28700</v>
       </c>
       <c r="G38" s="23">
         <f>IF(OR(Config!$G$12="",D38=0),"",E38/D38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="24">
+        <v>0.667824074074074</v>
+      </c>
+      <c r="H38" s="24" t="str">
         <f>IF(Config!$G$12="","",REPT("█",ROUND(IFERROR(D38/MAX($D$35:$D$44),0)*20,0)))</f>
-        <v/>
+        <v>████████</v>
       </c>
     </row>
     <row r="39">
@@ -2301,165 +2301,165 @@
       <c r="A48" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="20" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,1)&gt;0,INDEX(Clientes!$A$5:$A$64,MATCH(LARGE(Clientes!$K$5:$K$64,1),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C48" s="21">
+        <v>Clínica Bem-Estar</v>
+      </c>
+      <c r="C48" s="21" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,1)&gt;0,INDEX(Clientes!$B$5:$B$64,MATCH(LARGE(Clientes!$K$5:$K$64,1),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D48" s="21">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,1)&gt;0,INDEX(Clientes!$D$5:$D$64,MATCH(LARGE(Clientes!$K$5:$K$64,1),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E48" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,1)&gt;0,INDEX(Clientes!$F$5:$F$64,MATCH(LARGE(Clientes!$K$5:$K$64,1),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>39600</v>
       </c>
       <c r="F48" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,1)&gt;0,INDEX(Clientes!$G$5:$G$64,MATCH(LARGE(Clientes!$K$5:$K$64,1),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>34560</v>
       </c>
       <c r="G48" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,1)&gt;0,INDEX(Clientes!$H$5:$H$64,MATCH(LARGE(Clientes!$K$5:$K$64,1),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>5040</v>
       </c>
       <c r="H48" s="23">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,1)&gt;0,INDEX(Clientes!$I$5:$I$64,MATCH(LARGE(Clientes!$K$5:$K$64,1),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>0.872727272727273</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="20" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,2)&gt;0,INDEX(Clientes!$A$5:$A$64,MATCH(LARGE(Clientes!$K$5:$K$64,2),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C49" s="21">
+        <v>Oficina Mecânica Central</v>
+      </c>
+      <c r="C49" s="21" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,2)&gt;0,INDEX(Clientes!$B$5:$B$64,MATCH(LARGE(Clientes!$K$5:$K$64,2),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D49" s="21">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,2)&gt;0,INDEX(Clientes!$D$5:$D$64,MATCH(LARGE(Clientes!$K$5:$K$64,2),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E49" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,2)&gt;0,INDEX(Clientes!$F$5:$F$64,MATCH(LARGE(Clientes!$K$5:$K$64,2),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="F49" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,2)&gt;0,INDEX(Clientes!$G$5:$G$64,MATCH(LARGE(Clientes!$K$5:$K$64,2),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>31500</v>
       </c>
       <c r="G49" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,2)&gt;0,INDEX(Clientes!$H$5:$H$64,MATCH(LARGE(Clientes!$K$5:$K$64,2),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="H49" s="23">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,2)&gt;0,INDEX(Clientes!$I$5:$I$64,MATCH(LARGE(Clientes!$K$5:$K$64,2),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>0.875</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="20" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,3)&gt;0,INDEX(Clientes!$A$5:$A$64,MATCH(LARGE(Clientes!$K$5:$K$64,3),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C50" s="21">
+        <v>Construtora Horizonte</v>
+      </c>
+      <c r="C50" s="21" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,3)&gt;0,INDEX(Clientes!$B$5:$B$64,MATCH(LARGE(Clientes!$K$5:$K$64,3),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D50" s="21">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,3)&gt;0,INDEX(Clientes!$D$5:$D$64,MATCH(LARGE(Clientes!$K$5:$K$64,3),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E50" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,3)&gt;0,INDEX(Clientes!$F$5:$F$64,MATCH(LARGE(Clientes!$K$5:$K$64,3),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>33500</v>
       </c>
       <c r="F50" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,3)&gt;0,INDEX(Clientes!$G$5:$G$64,MATCH(LARGE(Clientes!$K$5:$K$64,3),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>24300</v>
       </c>
       <c r="G50" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,3)&gt;0,INDEX(Clientes!$H$5:$H$64,MATCH(LARGE(Clientes!$K$5:$K$64,3),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>9200</v>
       </c>
       <c r="H50" s="23">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,3)&gt;0,INDEX(Clientes!$I$5:$I$64,MATCH(LARGE(Clientes!$K$5:$K$64,3),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>0.725373134328358</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="20" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,4)&gt;0,INDEX(Clientes!$A$5:$A$64,MATCH(LARGE(Clientes!$K$5:$K$64,4),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="21">
+        <v>Agência Prisma</v>
+      </c>
+      <c r="C51" s="21" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,4)&gt;0,INDEX(Clientes!$B$5:$B$64,MATCH(LARGE(Clientes!$K$5:$K$64,4),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D51" s="21">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,4)&gt;0,INDEX(Clientes!$D$5:$D$64,MATCH(LARGE(Clientes!$K$5:$K$64,4),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E51" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,4)&gt;0,INDEX(Clientes!$F$5:$F$64,MATCH(LARGE(Clientes!$K$5:$K$64,4),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>31000</v>
       </c>
       <c r="F51" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,4)&gt;0,INDEX(Clientes!$G$5:$G$64,MATCH(LARGE(Clientes!$K$5:$K$64,4),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>25900</v>
       </c>
       <c r="G51" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,4)&gt;0,INDEX(Clientes!$H$5:$H$64,MATCH(LARGE(Clientes!$K$5:$K$64,4),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>5100</v>
       </c>
       <c r="H51" s="23">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,4)&gt;0,INDEX(Clientes!$I$5:$I$64,MATCH(LARGE(Clientes!$K$5:$K$64,4),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>0.835483870967742</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="20" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,5)&gt;0,INDEX(Clientes!$A$5:$A$64,MATCH(LARGE(Clientes!$K$5:$K$64,5),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="21">
+        <v>Padaria do Sol Ltda</v>
+      </c>
+      <c r="C52" s="21" t="str">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,5)&gt;0,INDEX(Clientes!$B$5:$B$64,MATCH(LARGE(Clientes!$K$5:$K$64,5),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D52" s="21">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,5)&gt;0,INDEX(Clientes!$D$5:$D$64,MATCH(LARGE(Clientes!$K$5:$K$64,5),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E52" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,5)&gt;0,INDEX(Clientes!$F$5:$F$64,MATCH(LARGE(Clientes!$K$5:$K$64,5),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="F52" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,5)&gt;0,INDEX(Clientes!$G$5:$G$64,MATCH(LARGE(Clientes!$K$5:$K$64,5),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>16500</v>
       </c>
       <c r="G52" s="22">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,5)&gt;0,INDEX(Clientes!$H$5:$H$64,MATCH(LARGE(Clientes!$K$5:$K$64,5),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>13500</v>
       </c>
       <c r="H52" s="23">
         <f>IFERROR(IF(LARGE(Clientes!$K$5:$K$64,5)&gt;0,INDEX(Clientes!$I$5:$I$64,MATCH(LARGE(Clientes!$K$5:$K$64,5),Clientes!$K$5:$K$64,0)),""),"")</f>
-        <v/>
+        <v>0.55</v>
       </c>
     </row>
     <row r="54">
@@ -2509,23 +2509,23 @@
       </c>
       <c r="B56" s="21">
         <f>COUNTIFS(Casos!$L$5:$L$204,A56)</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="C56" s="22">
         <f>SUMIFS(Casos!$H$5:$H$204,Casos!$L$5:$L$204,A56)</f>
-        <v/>
+        <v>307900</v>
       </c>
       <c r="D56" s="22">
         <f>SUMIFS(Casos!$I$5:$I$204,Casos!$L$5:$L$204,A56)</f>
-        <v/>
+        <v>195910</v>
       </c>
       <c r="E56" s="22">
         <f>C56-D56</f>
-        <v/>
+        <v>111990</v>
       </c>
       <c r="F56" s="23">
         <f>IFERROR(D56/C56,0)</f>
-        <v/>
+        <v>0.636278012341669</v>
       </c>
     </row>
     <row r="57">
@@ -2536,29 +2536,36 @@
       </c>
       <c r="B57" s="21">
         <f>COUNTIFS(Casos!$L$5:$L$204,A57)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C57" s="22">
         <f>SUMIFS(Casos!$H$5:$H$204,Casos!$L$5:$L$204,A57)</f>
-        <v/>
+        <v>76000</v>
       </c>
       <c r="D57" s="22">
         <f>SUMIFS(Casos!$I$5:$I$204,Casos!$L$5:$L$204,A57)</f>
-        <v/>
+        <v>76000</v>
       </c>
       <c r="E57" s="22">
         <f>C57-D57</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F57" s="23">
         <f>IFERROR(D57/C57,0)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="25" t="inlineStr">
         <is>
           <t>A receber dos casos encerrados é honorário devido e ainda não recebido: vale conferir antes de arquivar. Fonte: abas Casos e Clientes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>A receber (carteira) = contratado − recebido. Inclui o êxito esperado dos casos ativos e o que ainda não virou parcela; não é atraso. O que já venceu e não foi pago está na planilha 14 (Vencido).</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2645,7 @@
       </c>
       <c r="B5" s="28">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
     </row>
     <row r="6">
@@ -2950,35 +2957,35 @@
       </c>
       <c r="D5" s="21">
         <f>IF(A5="","",COUNTIFS(Casos!$B$5:$B$204,A5))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E5" s="21">
         <f>IF(A5="","",COUNTIFS(Casos!$B$5:$B$204,A5,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F5" s="22">
         <f>IF(A5="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A5))</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="G5" s="22">
         <f>IF(A5="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A5))</f>
-        <v/>
+        <v>16500</v>
       </c>
       <c r="H5" s="22">
         <f>IF(A5="","",F5-G5)</f>
-        <v/>
+        <v>13500</v>
       </c>
       <c r="I5" s="23">
         <f>IF(OR(A5="",F5=0),"",G5/F5)</f>
-        <v/>
+        <v>0.55</v>
       </c>
       <c r="J5" s="30">
-        <f>IF(A5="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A5)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A5)))</f>
-        <v/>
+        <f>IF(A5="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A5)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A5)*Casos!$K$5:$K$204))))</f>
+        <v>46202.0</v>
       </c>
       <c r="K5" s="31">
         <f>IF(OR(A5="",F5=0),0,F5-ROW()/100000)</f>
-        <v/>
+        <v>29999.99995</v>
       </c>
     </row>
     <row r="6">
@@ -2999,35 +3006,35 @@
       </c>
       <c r="D6" s="21">
         <f>IF(A6="","",COUNTIFS(Casos!$B$5:$B$204,A6))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E6" s="21">
         <f>IF(A6="","",COUNTIFS(Casos!$B$5:$B$204,A6,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F6" s="22">
         <f>IF(A6="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A6))</f>
-        <v/>
+        <v>14500</v>
       </c>
       <c r="G6" s="22">
         <f>IF(A6="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A6))</f>
-        <v/>
+        <v>8500</v>
       </c>
       <c r="H6" s="22">
         <f>IF(A6="","",F6-G6)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="I6" s="23">
         <f>IF(OR(A6="",F6=0),"",G6/F6)</f>
-        <v/>
+        <v>0.586206896551724</v>
       </c>
       <c r="J6" s="30">
-        <f>IF(A6="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A6)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A6)))</f>
-        <v/>
+        <f>IF(A6="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A6)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A6)*Casos!$K$5:$K$204))))</f>
+        <v>46210.0</v>
       </c>
       <c r="K6" s="31">
         <f>IF(OR(A6="",F6=0),0,F6-ROW()/100000)</f>
-        <v/>
+        <v>14499.99994</v>
       </c>
     </row>
     <row r="7">
@@ -3048,35 +3055,35 @@
       </c>
       <c r="D7" s="21">
         <f>IF(A7="","",COUNTIFS(Casos!$B$5:$B$204,A7))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E7" s="21">
         <f>IF(A7="","",COUNTIFS(Casos!$B$5:$B$204,A7,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F7" s="22">
         <f>IF(A7="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A7))</f>
-        <v/>
+        <v>33500</v>
       </c>
       <c r="G7" s="22">
         <f>IF(A7="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A7))</f>
-        <v/>
+        <v>24300</v>
       </c>
       <c r="H7" s="22">
         <f>IF(A7="","",F7-G7)</f>
-        <v/>
+        <v>9200</v>
       </c>
       <c r="I7" s="23">
         <f>IF(OR(A7="",F7=0),"",G7/F7)</f>
-        <v/>
+        <v>0.725373134328358</v>
       </c>
       <c r="J7" s="30">
-        <f>IF(A7="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A7)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A7)))</f>
-        <v/>
+        <f>IF(A7="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A7)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A7)*Casos!$K$5:$K$204))))</f>
+        <v>46225.0</v>
       </c>
       <c r="K7" s="31">
         <f>IF(OR(A7="",F7=0),0,F7-ROW()/100000)</f>
-        <v/>
+        <v>33499.99993</v>
       </c>
     </row>
     <row r="8">
@@ -3097,35 +3104,35 @@
       </c>
       <c r="D8" s="21">
         <f>IF(A8="","",COUNTIFS(Casos!$B$5:$B$204,A8))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E8" s="21">
         <f>IF(A8="","",COUNTIFS(Casos!$B$5:$B$204,A8,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F8" s="22">
         <f>IF(A8="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A8))</f>
-        <v/>
+        <v>13000</v>
       </c>
       <c r="G8" s="22">
         <f>IF(A8="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A8))</f>
-        <v/>
+        <v>7500</v>
       </c>
       <c r="H8" s="22">
         <f>IF(A8="","",F8-G8)</f>
-        <v/>
+        <v>5500</v>
       </c>
       <c r="I8" s="23">
         <f>IF(OR(A8="",F8=0),"",G8/F8)</f>
-        <v/>
+        <v>0.576923076923077</v>
       </c>
       <c r="J8" s="30">
-        <f>IF(A8="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A8)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A8)))</f>
-        <v/>
+        <f>IF(A8="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A8)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A8)*Casos!$K$5:$K$204))))</f>
+        <v>46231.0</v>
       </c>
       <c r="K8" s="31">
         <f>IF(OR(A8="",F8=0),0,F8-ROW()/100000)</f>
-        <v/>
+        <v>12999.99992</v>
       </c>
     </row>
     <row r="9">
@@ -3146,35 +3153,35 @@
       </c>
       <c r="D9" s="21">
         <f>IF(A9="","",COUNTIFS(Casos!$B$5:$B$204,A9))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E9" s="21">
         <f>IF(A9="","",COUNTIFS(Casos!$B$5:$B$204,A9,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F9" s="22">
         <f>IF(A9="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A9))</f>
-        <v/>
+        <v>14400</v>
       </c>
       <c r="G9" s="22">
         <f>IF(A9="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A9))</f>
-        <v/>
+        <v>8800</v>
       </c>
       <c r="H9" s="22">
         <f>IF(A9="","",F9-G9)</f>
-        <v/>
+        <v>5600</v>
       </c>
       <c r="I9" s="23">
         <f>IF(OR(A9="",F9=0),"",G9/F9)</f>
-        <v/>
+        <v>0.611111111111111</v>
       </c>
       <c r="J9" s="30">
-        <f>IF(A9="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A9)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A9)))</f>
-        <v/>
+        <f>IF(A9="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A9)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A9)*Casos!$K$5:$K$204))))</f>
+        <v>46245.0</v>
       </c>
       <c r="K9" s="31">
         <f>IF(OR(A9="",F9=0),0,F9-ROW()/100000)</f>
-        <v/>
+        <v>14399.99991</v>
       </c>
     </row>
     <row r="10">
@@ -3195,35 +3202,35 @@
       </c>
       <c r="D10" s="21">
         <f>IF(A10="","",COUNTIFS(Casos!$B$5:$B$204,A10))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E10" s="21">
         <f>IF(A10="","",COUNTIFS(Casos!$B$5:$B$204,A10,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F10" s="22">
         <f>IF(A10="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A10))</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="G10" s="22">
         <f>IF(A10="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A10))</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="H10" s="22">
         <f>IF(A10="","",F10-G10)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I10" s="23">
         <f>IF(OR(A10="",F10=0),"",G10/F10)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J10" s="30">
-        <f>IF(A10="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A10)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A10)))</f>
-        <v/>
+        <f>IF(A10="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A10)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A10)*Casos!$K$5:$K$204))))</f>
+        <v>45936.0</v>
       </c>
       <c r="K10" s="31">
         <f>IF(OR(A10="",F10=0),0,F10-ROW()/100000)</f>
-        <v/>
+        <v>6999.9999</v>
       </c>
     </row>
     <row r="11">
@@ -3244,35 +3251,35 @@
       </c>
       <c r="D11" s="21">
         <f>IF(A11="","",COUNTIFS(Casos!$B$5:$B$204,A11))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E11" s="21">
         <f>IF(A11="","",COUNTIFS(Casos!$B$5:$B$204,A11,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F11" s="22">
         <f>IF(A11="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A11))</f>
-        <v/>
+        <v>13500</v>
       </c>
       <c r="G11" s="22">
         <f>IF(A11="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A11))</f>
-        <v/>
+        <v>5300</v>
       </c>
       <c r="H11" s="22">
         <f>IF(A11="","",F11-G11)</f>
-        <v/>
+        <v>8200</v>
       </c>
       <c r="I11" s="23">
         <f>IF(OR(A11="",F11=0),"",G11/F11)</f>
-        <v/>
+        <v>0.392592592592593</v>
       </c>
       <c r="J11" s="30">
-        <f>IF(A11="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A11)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A11)))</f>
-        <v/>
+        <f>IF(A11="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A11)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A11)*Casos!$K$5:$K$204))))</f>
+        <v>46034.0</v>
       </c>
       <c r="K11" s="31">
         <f>IF(OR(A11="",F11=0),0,F11-ROW()/100000)</f>
-        <v/>
+        <v>13499.99989</v>
       </c>
     </row>
     <row r="12">
@@ -3293,35 +3300,35 @@
       </c>
       <c r="D12" s="21">
         <f>IF(A12="","",COUNTIFS(Casos!$B$5:$B$204,A12))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E12" s="21">
         <f>IF(A12="","",COUNTIFS(Casos!$B$5:$B$204,A12,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F12" s="22">
         <f>IF(A12="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A12))</f>
-        <v/>
+        <v>25200</v>
       </c>
       <c r="G12" s="22">
         <f>IF(A12="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A12))</f>
-        <v/>
+        <v>22200</v>
       </c>
       <c r="H12" s="22">
         <f>IF(A12="","",F12-G12)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="I12" s="23">
         <f>IF(OR(A12="",F12=0),"",G12/F12)</f>
-        <v/>
+        <v>0.880952380952381</v>
       </c>
       <c r="J12" s="30">
-        <f>IF(A12="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A12)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A12)))</f>
-        <v/>
+        <f>IF(A12="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A12)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A12)*Casos!$K$5:$K$204))))</f>
+        <v>46146.0</v>
       </c>
       <c r="K12" s="31">
         <f>IF(OR(A12="",F12=0),0,F12-ROW()/100000)</f>
-        <v/>
+        <v>25199.99988</v>
       </c>
     </row>
     <row r="13">
@@ -3342,35 +3349,35 @@
       </c>
       <c r="D13" s="21">
         <f>IF(A13="","",COUNTIFS(Casos!$B$5:$B$204,A13))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E13" s="21">
         <f>IF(A13="","",COUNTIFS(Casos!$B$5:$B$204,A13,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F13" s="22">
         <f>IF(A13="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A13))</f>
-        <v/>
+        <v>39600</v>
       </c>
       <c r="G13" s="22">
         <f>IF(A13="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A13))</f>
-        <v/>
+        <v>34560</v>
       </c>
       <c r="H13" s="22">
         <f>IF(A13="","",F13-G13)</f>
-        <v/>
+        <v>5040</v>
       </c>
       <c r="I13" s="23">
         <f>IF(OR(A13="",F13=0),"",G13/F13)</f>
-        <v/>
+        <v>0.872727272727273</v>
       </c>
       <c r="J13" s="30">
-        <f>IF(A13="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A13)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A13)))</f>
-        <v/>
+        <f>IF(A13="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A13)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A13)*Casos!$K$5:$K$204))))</f>
+        <v>46160.0</v>
       </c>
       <c r="K13" s="31">
         <f>IF(OR(A13="",F13=0),0,F13-ROW()/100000)</f>
-        <v/>
+        <v>39599.99987</v>
       </c>
     </row>
     <row r="14">
@@ -3391,35 +3398,35 @@
       </c>
       <c r="D14" s="21">
         <f>IF(A14="","",COUNTIFS(Casos!$B$5:$B$204,A14))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E14" s="21">
         <f>IF(A14="","",COUNTIFS(Casos!$B$5:$B$204,A14,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F14" s="22">
         <f>IF(A14="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A14))</f>
-        <v/>
+        <v>16400</v>
       </c>
       <c r="G14" s="22">
         <f>IF(A14="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A14))</f>
-        <v/>
+        <v>14150</v>
       </c>
       <c r="H14" s="22">
         <f>IF(A14="","",F14-G14)</f>
-        <v/>
+        <v>2250</v>
       </c>
       <c r="I14" s="23">
         <f>IF(OR(A14="",F14=0),"",G14/F14)</f>
-        <v/>
+        <v>0.862804878048781</v>
       </c>
       <c r="J14" s="30">
-        <f>IF(A14="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A14)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A14)))</f>
-        <v/>
+        <f>IF(A14="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A14)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A14)*Casos!$K$5:$K$204))))</f>
+        <v>46253.0</v>
       </c>
       <c r="K14" s="31">
         <f>IF(OR(A14="",F14=0),0,F14-ROW()/100000)</f>
-        <v/>
+        <v>16399.99986</v>
       </c>
     </row>
     <row r="15">
@@ -3440,35 +3447,35 @@
       </c>
       <c r="D15" s="21">
         <f>IF(A15="","",COUNTIFS(Casos!$B$5:$B$204,A15))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E15" s="21">
         <f>IF(A15="","",COUNTIFS(Casos!$B$5:$B$204,A15,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F15" s="22">
         <f>IF(A15="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A15))</f>
-        <v/>
+        <v>26900</v>
       </c>
       <c r="G15" s="22">
         <f>IF(A15="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A15))</f>
-        <v/>
+        <v>17900</v>
       </c>
       <c r="H15" s="22">
         <f>IF(A15="","",F15-G15)</f>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="I15" s="23">
         <f>IF(OR(A15="",F15=0),"",G15/F15)</f>
-        <v/>
+        <v>0.66542750929368</v>
       </c>
       <c r="J15" s="30">
-        <f>IF(A15="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A15)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A15)))</f>
-        <v/>
+        <f>IF(A15="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A15)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A15)*Casos!$K$5:$K$204))))</f>
+        <v>46216.0</v>
       </c>
       <c r="K15" s="31">
         <f>IF(OR(A15="",F15=0),0,F15-ROW()/100000)</f>
-        <v/>
+        <v>26899.99985</v>
       </c>
     </row>
     <row r="16">
@@ -3489,35 +3496,35 @@
       </c>
       <c r="D16" s="21">
         <f>IF(A16="","",COUNTIFS(Casos!$B$5:$B$204,A16))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E16" s="21">
         <f>IF(A16="","",COUNTIFS(Casos!$B$5:$B$204,A16,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F16" s="22">
         <f>IF(A16="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A16))</f>
-        <v/>
+        <v>15600</v>
       </c>
       <c r="G16" s="22">
         <f>IF(A16="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A16))</f>
-        <v/>
+        <v>13500</v>
       </c>
       <c r="H16" s="22">
         <f>IF(A16="","",F16-G16)</f>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="I16" s="23">
         <f>IF(OR(A16="",F16=0),"",G16/F16)</f>
-        <v/>
+        <v>0.865384615384615</v>
       </c>
       <c r="J16" s="30">
-        <f>IF(A16="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A16)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A16)))</f>
-        <v/>
+        <f>IF(A16="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A16)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A16)*Casos!$K$5:$K$204))))</f>
+        <v>46181.0</v>
       </c>
       <c r="K16" s="31">
         <f>IF(OR(A16="",F16=0),0,F16-ROW()/100000)</f>
-        <v/>
+        <v>15599.99984</v>
       </c>
     </row>
     <row r="17">
@@ -3538,35 +3545,35 @@
       </c>
       <c r="D17" s="21">
         <f>IF(A17="","",COUNTIFS(Casos!$B$5:$B$204,A17))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E17" s="21">
         <f>IF(A17="","",COUNTIFS(Casos!$B$5:$B$204,A17,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F17" s="22">
         <f>IF(A17="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A17))</f>
-        <v/>
+        <v>23200</v>
       </c>
       <c r="G17" s="22">
         <f>IF(A17="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A17))</f>
-        <v/>
+        <v>8200</v>
       </c>
       <c r="H17" s="22">
         <f>IF(A17="","",F17-G17)</f>
-        <v/>
+        <v>15000</v>
       </c>
       <c r="I17" s="23">
         <f>IF(OR(A17="",F17=0),"",G17/F17)</f>
-        <v/>
+        <v>0.353448275862069</v>
       </c>
       <c r="J17" s="30">
-        <f>IF(A17="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A17)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A17)))</f>
-        <v/>
+        <f>IF(A17="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A17)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A17)*Casos!$K$5:$K$204))))</f>
+        <v>46237.0</v>
       </c>
       <c r="K17" s="31">
         <f>IF(OR(A17="",F17=0),0,F17-ROW()/100000)</f>
-        <v/>
+        <v>23199.99983</v>
       </c>
     </row>
     <row r="18">
@@ -3587,35 +3594,35 @@
       </c>
       <c r="D18" s="21">
         <f>IF(A18="","",COUNTIFS(Casos!$B$5:$B$204,A18))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E18" s="21">
         <f>IF(A18="","",COUNTIFS(Casos!$B$5:$B$204,A18,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F18" s="22">
         <f>IF(A18="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A18))</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="G18" s="22">
         <f>IF(A18="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A18))</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="H18" s="22">
         <f>IF(A18="","",F18-G18)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="I18" s="23">
         <f>IF(OR(A18="",F18=0),"",G18/F18)</f>
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="J18" s="30">
-        <f>IF(A18="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A18)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A18)))</f>
-        <v/>
+        <f>IF(A18="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A18)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A18)*Casos!$K$5:$K$204))))</f>
+        <v>46048.0</v>
       </c>
       <c r="K18" s="31">
         <f>IF(OR(A18="",F18=0),0,F18-ROW()/100000)</f>
-        <v/>
+        <v>9999.99982</v>
       </c>
     </row>
     <row r="19">
@@ -3636,35 +3643,35 @@
       </c>
       <c r="D19" s="21">
         <f>IF(A19="","",COUNTIFS(Casos!$B$5:$B$204,A19))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E19" s="21">
         <f>IF(A19="","",COUNTIFS(Casos!$B$5:$B$204,A19,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F19" s="22">
         <f>IF(A19="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A19))</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="G19" s="22">
         <f>IF(A19="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A19))</f>
-        <v/>
+        <v>31500</v>
       </c>
       <c r="H19" s="22">
         <f>IF(A19="","",F19-G19)</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="I19" s="23">
         <f>IF(OR(A19="",F19=0),"",G19/F19)</f>
-        <v/>
+        <v>0.875</v>
       </c>
       <c r="J19" s="30">
-        <f>IF(A19="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A19)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A19)))</f>
-        <v/>
+        <f>IF(A19="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A19)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A19)*Casos!$K$5:$K$204))))</f>
+        <v>46125.0</v>
       </c>
       <c r="K19" s="31">
         <f>IF(OR(A19="",F19=0),0,F19-ROW()/100000)</f>
-        <v/>
+        <v>35999.99981</v>
       </c>
     </row>
     <row r="20">
@@ -3685,35 +3692,35 @@
       </c>
       <c r="D20" s="21">
         <f>IF(A20="","",COUNTIFS(Casos!$B$5:$B$204,A20))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E20" s="21">
         <f>IF(A20="","",COUNTIFS(Casos!$B$5:$B$204,A20,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F20" s="22">
         <f>IF(A20="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A20))</f>
-        <v/>
+        <v>19600</v>
       </c>
       <c r="G20" s="22">
         <f>IF(A20="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A20))</f>
-        <v/>
+        <v>15600</v>
       </c>
       <c r="H20" s="22">
         <f>IF(A20="","",F20-G20)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="I20" s="23">
         <f>IF(OR(A20="",F20=0),"",G20/F20)</f>
-        <v/>
+        <v>0.795918367346939</v>
       </c>
       <c r="J20" s="30">
-        <f>IF(A20="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A20)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A20)))</f>
-        <v/>
+        <f>IF(A20="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A20)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A20)*Casos!$K$5:$K$204))))</f>
+        <v>46202.0</v>
       </c>
       <c r="K20" s="31">
         <f>IF(OR(A20="",F20=0),0,F20-ROW()/100000)</f>
-        <v/>
+        <v>19599.9998</v>
       </c>
     </row>
     <row r="21">
@@ -3734,35 +3741,35 @@
       </c>
       <c r="D21" s="21">
         <f>IF(A21="","",COUNTIFS(Casos!$B$5:$B$204,A21))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E21" s="21">
         <f>IF(A21="","",COUNTIFS(Casos!$B$5:$B$204,A21,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F21" s="22">
         <f>IF(A21="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A21))</f>
-        <v/>
+        <v>31000</v>
       </c>
       <c r="G21" s="22">
         <f>IF(A21="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A21))</f>
-        <v/>
+        <v>25900</v>
       </c>
       <c r="H21" s="22">
         <f>IF(A21="","",F21-G21)</f>
-        <v/>
+        <v>5100</v>
       </c>
       <c r="I21" s="23">
         <f>IF(OR(A21="",F21=0),"",G21/F21)</f>
-        <v/>
+        <v>0.835483870967742</v>
       </c>
       <c r="J21" s="30">
-        <f>IF(A21="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A21)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A21)))</f>
-        <v/>
+        <f>IF(A21="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A21)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A21)*Casos!$K$5:$K$204))))</f>
+        <v>46118.0</v>
       </c>
       <c r="K21" s="31">
         <f>IF(OR(A21="",F21=0),0,F21-ROW()/100000)</f>
-        <v/>
+        <v>30999.99979</v>
       </c>
     </row>
     <row r="22">
@@ -3783,35 +3790,35 @@
       </c>
       <c r="D22" s="21">
         <f>IF(A22="","",COUNTIFS(Casos!$B$5:$B$204,A22))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E22" s="21">
         <f>IF(A22="","",COUNTIFS(Casos!$B$5:$B$204,A22,Casos!$L$5:$L$204,"Ativo"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F22" s="22">
         <f>IF(A22="","",SUMIFS(Casos!$H$5:$H$204,Casos!$B$5:$B$204,A22))</f>
-        <v/>
+        <v>14500</v>
       </c>
       <c r="G22" s="22">
         <f>IF(A22="","",SUMIFS(Casos!$I$5:$I$204,Casos!$B$5:$B$204,A22))</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="H22" s="22">
         <f>IF(A22="","",F22-G22)</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="I22" s="23">
         <f>IF(OR(A22="",F22=0),"",G22/F22)</f>
-        <v/>
+        <v>0.310344827586207</v>
       </c>
       <c r="J22" s="30">
-        <f>IF(A22="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A22)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A22)))</f>
-        <v/>
+        <f>IF(A22="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A22)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A22)*Casos!$K$5:$K$204))))</f>
+        <v>46195.0</v>
       </c>
       <c r="K22" s="31">
         <f>IF(OR(A22="",F22=0),0,F22-ROW()/100000)</f>
-        <v/>
+        <v>14499.99978</v>
       </c>
     </row>
     <row r="23">
@@ -3843,12 +3850,12 @@
         <v/>
       </c>
       <c r="J23" s="30">
-        <f>IF(A23="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A23)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A23)))</f>
+        <f>IF(A23="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A23)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A23)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K23" s="31">
         <f>IF(OR(A23="",F23=0),0,F23-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3880,12 +3887,12 @@
         <v/>
       </c>
       <c r="J24" s="30">
-        <f>IF(A24="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A24)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A24)))</f>
+        <f>IF(A24="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A24)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A24)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K24" s="31">
         <f>IF(OR(A24="",F24=0),0,F24-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3917,12 +3924,12 @@
         <v/>
       </c>
       <c r="J25" s="30">
-        <f>IF(A25="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A25)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A25)))</f>
+        <f>IF(A25="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A25)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A25)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K25" s="31">
         <f>IF(OR(A25="",F25=0),0,F25-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3954,12 +3961,12 @@
         <v/>
       </c>
       <c r="J26" s="30">
-        <f>IF(A26="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A26)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A26)))</f>
+        <f>IF(A26="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A26)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A26)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K26" s="31">
         <f>IF(OR(A26="",F26=0),0,F26-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3991,12 +3998,12 @@
         <v/>
       </c>
       <c r="J27" s="30">
-        <f>IF(A27="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A27)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A27)))</f>
+        <f>IF(A27="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A27)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A27)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K27" s="31">
         <f>IF(OR(A27="",F27=0),0,F27-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4028,12 +4035,12 @@
         <v/>
       </c>
       <c r="J28" s="30">
-        <f>IF(A28="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A28)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A28)))</f>
+        <f>IF(A28="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A28)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A28)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K28" s="31">
         <f>IF(OR(A28="",F28=0),0,F28-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4065,12 +4072,12 @@
         <v/>
       </c>
       <c r="J29" s="30">
-        <f>IF(A29="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A29)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A29)))</f>
+        <f>IF(A29="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A29)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A29)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K29" s="31">
         <f>IF(OR(A29="",F29=0),0,F29-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4102,12 +4109,12 @@
         <v/>
       </c>
       <c r="J30" s="30">
-        <f>IF(A30="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A30)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A30)))</f>
+        <f>IF(A30="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A30)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A30)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K30" s="31">
         <f>IF(OR(A30="",F30=0),0,F30-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4139,12 +4146,12 @@
         <v/>
       </c>
       <c r="J31" s="30">
-        <f>IF(A31="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A31)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A31)))</f>
+        <f>IF(A31="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A31)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A31)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K31" s="31">
         <f>IF(OR(A31="",F31=0),0,F31-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4176,12 +4183,12 @@
         <v/>
       </c>
       <c r="J32" s="30">
-        <f>IF(A32="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A32)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A32)))</f>
+        <f>IF(A32="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A32)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A32)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K32" s="31">
         <f>IF(OR(A32="",F32=0),0,F32-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4213,12 +4220,12 @@
         <v/>
       </c>
       <c r="J33" s="30">
-        <f>IF(A33="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A33)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A33)))</f>
+        <f>IF(A33="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A33)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A33)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K33" s="31">
         <f>IF(OR(A33="",F33=0),0,F33-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4250,12 +4257,12 @@
         <v/>
       </c>
       <c r="J34" s="30">
-        <f>IF(A34="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A34)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A34)))</f>
+        <f>IF(A34="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A34)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A34)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K34" s="31">
         <f>IF(OR(A34="",F34=0),0,F34-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4287,12 +4294,12 @@
         <v/>
       </c>
       <c r="J35" s="30">
-        <f>IF(A35="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A35)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A35)))</f>
+        <f>IF(A35="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A35)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A35)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K35" s="31">
         <f>IF(OR(A35="",F35=0),0,F35-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4324,12 +4331,12 @@
         <v/>
       </c>
       <c r="J36" s="30">
-        <f>IF(A36="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A36)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A36)))</f>
+        <f>IF(A36="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A36)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A36)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K36" s="31">
         <f>IF(OR(A36="",F36=0),0,F36-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4361,12 +4368,12 @@
         <v/>
       </c>
       <c r="J37" s="30">
-        <f>IF(A37="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A37)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A37)))</f>
+        <f>IF(A37="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A37)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A37)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K37" s="31">
         <f>IF(OR(A37="",F37=0),0,F37-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4398,12 +4405,12 @@
         <v/>
       </c>
       <c r="J38" s="30">
-        <f>IF(A38="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A38)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A38)))</f>
+        <f>IF(A38="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A38)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A38)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K38" s="31">
         <f>IF(OR(A38="",F38=0),0,F38-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4435,12 +4442,12 @@
         <v/>
       </c>
       <c r="J39" s="30">
-        <f>IF(A39="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A39)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A39)))</f>
+        <f>IF(A39="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A39)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A39)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K39" s="31">
         <f>IF(OR(A39="",F39=0),0,F39-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4472,12 +4479,12 @@
         <v/>
       </c>
       <c r="J40" s="30">
-        <f>IF(A40="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A40)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A40)))</f>
+        <f>IF(A40="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A40)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A40)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K40" s="31">
         <f>IF(OR(A40="",F40=0),0,F40-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4509,12 +4516,12 @@
         <v/>
       </c>
       <c r="J41" s="30">
-        <f>IF(A41="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A41)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A41)))</f>
+        <f>IF(A41="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A41)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A41)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K41" s="31">
         <f>IF(OR(A41="",F41=0),0,F41-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4546,12 +4553,12 @@
         <v/>
       </c>
       <c r="J42" s="30">
-        <f>IF(A42="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A42)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A42)))</f>
+        <f>IF(A42="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A42)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A42)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K42" s="31">
         <f>IF(OR(A42="",F42=0),0,F42-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4583,12 +4590,12 @@
         <v/>
       </c>
       <c r="J43" s="30">
-        <f>IF(A43="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A43)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A43)))</f>
+        <f>IF(A43="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A43)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A43)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K43" s="31">
         <f>IF(OR(A43="",F43=0),0,F43-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4620,12 +4627,12 @@
         <v/>
       </c>
       <c r="J44" s="30">
-        <f>IF(A44="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A44)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A44)))</f>
+        <f>IF(A44="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A44)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A44)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K44" s="31">
         <f>IF(OR(A44="",F44=0),0,F44-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4657,12 +4664,12 @@
         <v/>
       </c>
       <c r="J45" s="30">
-        <f>IF(A45="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A45)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A45)))</f>
+        <f>IF(A45="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A45)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A45)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K45" s="31">
         <f>IF(OR(A45="",F45=0),0,F45-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4694,12 +4701,12 @@
         <v/>
       </c>
       <c r="J46" s="30">
-        <f>IF(A46="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A46)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A46)))</f>
+        <f>IF(A46="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A46)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A46)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K46" s="31">
         <f>IF(OR(A46="",F46=0),0,F46-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4731,12 +4738,12 @@
         <v/>
       </c>
       <c r="J47" s="30">
-        <f>IF(A47="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A47)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A47)))</f>
+        <f>IF(A47="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A47)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A47)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K47" s="31">
         <f>IF(OR(A47="",F47=0),0,F47-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4768,12 +4775,12 @@
         <v/>
       </c>
       <c r="J48" s="30">
-        <f>IF(A48="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A48)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A48)))</f>
+        <f>IF(A48="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A48)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A48)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K48" s="31">
         <f>IF(OR(A48="",F48=0),0,F48-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4805,12 +4812,12 @@
         <v/>
       </c>
       <c r="J49" s="30">
-        <f>IF(A49="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A49)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A49)))</f>
+        <f>IF(A49="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A49)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A49)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K49" s="31">
         <f>IF(OR(A49="",F49=0),0,F49-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4842,12 +4849,12 @@
         <v/>
       </c>
       <c r="J50" s="30">
-        <f>IF(A50="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A50)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A50)))</f>
+        <f>IF(A50="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A50)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A50)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K50" s="31">
         <f>IF(OR(A50="",F50=0),0,F50-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4879,12 +4886,12 @@
         <v/>
       </c>
       <c r="J51" s="30">
-        <f>IF(A51="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A51)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A51)))</f>
+        <f>IF(A51="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A51)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A51)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K51" s="31">
         <f>IF(OR(A51="",F51=0),0,F51-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4916,12 +4923,12 @@
         <v/>
       </c>
       <c r="J52" s="30">
-        <f>IF(A52="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A52)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A52)))</f>
+        <f>IF(A52="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A52)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A52)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K52" s="31">
         <f>IF(OR(A52="",F52=0),0,F52-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4953,12 +4960,12 @@
         <v/>
       </c>
       <c r="J53" s="30">
-        <f>IF(A53="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A53)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A53)))</f>
+        <f>IF(A53="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A53)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A53)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K53" s="31">
         <f>IF(OR(A53="",F53=0),0,F53-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4990,12 +4997,12 @@
         <v/>
       </c>
       <c r="J54" s="30">
-        <f>IF(A54="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A54)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A54)))</f>
+        <f>IF(A54="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A54)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A54)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K54" s="31">
         <f>IF(OR(A54="",F54=0),0,F54-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5027,12 +5034,12 @@
         <v/>
       </c>
       <c r="J55" s="30">
-        <f>IF(A55="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A55)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A55)))</f>
+        <f>IF(A55="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A55)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A55)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K55" s="31">
         <f>IF(OR(A55="",F55=0),0,F55-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5064,12 +5071,12 @@
         <v/>
       </c>
       <c r="J56" s="30">
-        <f>IF(A56="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A56)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A56)))</f>
+        <f>IF(A56="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A56)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A56)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K56" s="31">
         <f>IF(OR(A56="",F56=0),0,F56-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5101,12 +5108,12 @@
         <v/>
       </c>
       <c r="J57" s="30">
-        <f>IF(A57="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A57)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A57)))</f>
+        <f>IF(A57="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A57)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A57)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K57" s="31">
         <f>IF(OR(A57="",F57=0),0,F57-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5138,12 +5145,12 @@
         <v/>
       </c>
       <c r="J58" s="30">
-        <f>IF(A58="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A58)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A58)))</f>
+        <f>IF(A58="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A58)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A58)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K58" s="31">
         <f>IF(OR(A58="",F58=0),0,F58-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5175,12 +5182,12 @@
         <v/>
       </c>
       <c r="J59" s="30">
-        <f>IF(A59="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A59)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A59)))</f>
+        <f>IF(A59="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A59)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A59)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K59" s="31">
         <f>IF(OR(A59="",F59=0),0,F59-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5212,12 +5219,12 @@
         <v/>
       </c>
       <c r="J60" s="30">
-        <f>IF(A60="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A60)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A60)))</f>
+        <f>IF(A60="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A60)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A60)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K60" s="31">
         <f>IF(OR(A60="",F60=0),0,F60-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5249,12 +5256,12 @@
         <v/>
       </c>
       <c r="J61" s="30">
-        <f>IF(A61="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A61)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A61)))</f>
+        <f>IF(A61="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A61)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A61)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K61" s="31">
         <f>IF(OR(A61="",F61=0),0,F61-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5286,12 +5293,12 @@
         <v/>
       </c>
       <c r="J62" s="30">
-        <f>IF(A62="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A62)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A62)))</f>
+        <f>IF(A62="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A62)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A62)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K62" s="31">
         <f>IF(OR(A62="",F62=0),0,F62-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5323,12 +5330,12 @@
         <v/>
       </c>
       <c r="J63" s="30">
-        <f>IF(A63="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A63)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A63)))</f>
+        <f>IF(A63="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A63)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A63)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K63" s="31">
         <f>IF(OR(A63="",F63=0),0,F63-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5360,12 +5367,12 @@
         <v/>
       </c>
       <c r="J64" s="30">
-        <f>IF(A64="","",IF(_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A64)=0,"",_xlfn.MAXIFS(Casos!$K$5:$K$204,Casos!$B$5:$B$204,A64)))</f>
+        <f>IF(A64="","",IF(SUMPRODUCT(MAX((Casos!$B$5:$B$204=A64)*Casos!$K$5:$K$204))=0,"",SUMPRODUCT(MAX((Casos!$B$5:$B$204=A64)*Casos!$K$5:$K$204))))</f>
         <v/>
       </c>
       <c r="K64" s="31">
         <f>IF(OR(A64="",F64=0),0,F64-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5426,7 +5433,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Uma linha por caso. Cliente, área, fase, responsável e modalidade vêm de listas; tipo, a receber e situação são calculados.</t>
+          <t>Uma linha por caso: esta aba é a fonte do cadastro de casos do kit (as planilhas 01, 02, 04, 08, 14 e 16 copiam daqui). Cliente, área, fase, responsável e modalidade vêm de listas; tipo, a receber e situação são calculados.</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5507,7 @@
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>9236009-85.2026.8.26.0452</t>
+          <t>CONS-2026-01</t>
         </is>
       </c>
       <c r="B5" s="27" t="inlineStr">
@@ -5508,9 +5515,9 @@
           <t>Padaria do Sol Ltda</t>
         </is>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="21" t="str">
         <f>IF(B5="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B5,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
@@ -5519,7 +5526,7 @@
       </c>
       <c r="E5" s="29" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
@@ -5529,35 +5536,35 @@
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H5" s="32" t="n">
-        <v>14400</v>
+        <v>18000</v>
       </c>
       <c r="I5" s="32" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="J5" s="22">
         <f>IF(B5="","",H5-I5)</f>
-        <v/>
+        <v>13500</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>46154</v>
-      </c>
-      <c r="L5" s="21">
+        <v>46202</v>
+      </c>
+      <c r="L5" s="21" t="str">
         <f>IF(B5="","",IF(E5=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M5" s="23">
         <f>IF(OR(B5="",H5=0,H5=""),"",I5/H5)</f>
-        <v/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>9225646-96.2026.8.26.0322</t>
+          <t>2998500-50.2026.8.26.0515</t>
         </is>
       </c>
       <c r="B6" s="27" t="inlineStr">
@@ -5565,9 +5572,9 @@
           <t>Ana Beatriz Moreira</t>
         </is>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="21" t="str">
         <f>IF(B6="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B6,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
@@ -5576,7 +5583,7 @@
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
@@ -5586,35 +5593,35 @@
       </c>
       <c r="G6" s="29" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="H6" s="32" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="J6" s="22">
         <f>IF(B6="","",H6-I6)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="K6" s="33" t="n">
-        <v>46146</v>
-      </c>
-      <c r="L6" s="21">
+        <v>46210</v>
+      </c>
+      <c r="L6" s="21" t="str">
         <f>IF(B6="","",IF(E6=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M6" s="23">
         <f>IF(OR(B6="",H6=0,H6=""),"",I6/H6)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>6710873-21.2025.8.26.0571</t>
+          <t>9586960-92.2026.8.26.0106</t>
         </is>
       </c>
       <c r="B7" s="27" t="inlineStr">
@@ -5622,9 +5629,9 @@
           <t>Construtora Horizonte</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="21" t="str">
         <f>IF(B7="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B7,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
@@ -5633,7 +5640,7 @@
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F7" s="29" t="inlineStr">
@@ -5647,31 +5654,31 @@
         </is>
       </c>
       <c r="H7" s="32" t="n">
-        <v>8100</v>
+        <v>15500</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>8100</v>
+        <v>6300</v>
       </c>
       <c r="J7" s="22">
         <f>IF(B7="","",H7-I7)</f>
-        <v/>
+        <v>9200</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>45894</v>
-      </c>
-      <c r="L7" s="21">
+        <v>46225</v>
+      </c>
+      <c r="L7" s="21" t="str">
         <f>IF(B7="","",IF(E7=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M7" s="23">
         <f>IF(OR(B7="",H7=0,H7=""),"",I7/H7)</f>
-        <v/>
+        <v>0.406451612903226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>8735513-64.2025.8.26.0093</t>
+          <t>4746093-86.2026.8.26.0637</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
@@ -5679,9 +5686,9 @@
           <t>Carlos Eduardo Nunes</t>
         </is>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="21" t="str">
         <f>IF(B8="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B8,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
@@ -5690,7 +5697,7 @@
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F8" s="29" t="inlineStr">
@@ -5700,35 +5707,35 @@
       </c>
       <c r="G8" s="29" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H8" s="32" t="n">
-        <v>5700</v>
+        <v>5400</v>
       </c>
       <c r="I8" s="32" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="J8" s="22">
         <f>IF(B8="","",H8-I8)</f>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="K8" s="33" t="n">
-        <v>45943</v>
-      </c>
-      <c r="L8" s="21">
+        <v>46231</v>
+      </c>
+      <c r="L8" s="21" t="str">
         <f>IF(B8="","",IF(E8=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M8" s="23">
         <f>IF(OR(B8="",H8=0,H8=""),"",I8/H8)</f>
-        <v/>
+        <v>0.722222222222222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>9802211-43.2025.8.26.0431</t>
+          <t>CONS-2026-02</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
@@ -5736,9 +5743,9 @@
           <t>Loja Verde Comércio</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="21" t="str">
         <f>IF(B9="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B9,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
@@ -5747,7 +5754,7 @@
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F9" s="29" t="inlineStr">
@@ -5757,59 +5764,59 @@
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H9" s="32" t="n">
-        <v>19600</v>
+        <v>8400</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>19600</v>
+        <v>2800</v>
       </c>
       <c r="J9" s="22">
         <f>IF(B9="","",H9-I9)</f>
-        <v/>
+        <v>5600</v>
       </c>
       <c r="K9" s="33" t="n">
-        <v>45824</v>
-      </c>
-      <c r="L9" s="21">
+        <v>46245</v>
+      </c>
+      <c r="L9" s="21" t="str">
         <f>IF(B9="","",IF(E9=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M9" s="23">
         <f>IF(OR(B9="",H9=0,H9=""),"",I9/H9)</f>
-        <v/>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>9778116-95.2026.8.26.0106</t>
+          <t>CONS-2026-03</t>
         </is>
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
-        </is>
-      </c>
-      <c r="C10" s="21">
+          <t>Marcos Vinícius Teles</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="str">
         <f>IF(B10="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B10,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="E10" s="29" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
@@ -5818,273 +5825,273 @@
         </is>
       </c>
       <c r="H10" s="32" t="n">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="I10" s="32" t="n">
-        <v>9000</v>
+        <v>2250</v>
       </c>
       <c r="J10" s="22">
         <f>IF(B10="","",H10-I10)</f>
-        <v/>
+        <v>2250</v>
       </c>
       <c r="K10" s="33" t="n">
-        <v>46127</v>
-      </c>
-      <c r="L10" s="21">
+        <v>46253</v>
+      </c>
+      <c r="L10" s="21" t="str">
         <f>IF(B10="","",IF(E10=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M10" s="23">
         <f>IF(OR(B10="",H10=0,H10=""),"",I10/H10)</f>
-        <v/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>8875326-79.2026.8.26.0258</t>
+          <t>CONS-2026-04</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
-        </is>
-      </c>
-      <c r="C11" s="21">
+          <t>Escola Aurora</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="str">
         <f>IF(B11="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B11,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H11" s="32" t="n">
-        <v>4600</v>
+        <v>13200</v>
       </c>
       <c r="I11" s="32" t="n">
-        <v>4600</v>
+        <v>2200</v>
       </c>
       <c r="J11" s="22">
         <f>IF(B11="","",H11-I11)</f>
-        <v/>
+        <v>11000</v>
       </c>
       <c r="K11" s="33" t="n">
-        <v>46025</v>
-      </c>
-      <c r="L11" s="21">
+        <v>46237</v>
+      </c>
+      <c r="L11" s="21" t="str">
         <f>IF(B11="","",IF(E11=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M11" s="23">
         <f>IF(OR(B11="",H11=0,H11=""),"",I11/H11)</f>
-        <v/>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>4397912-47.2025.8.26.0276</t>
+          <t>8056747-83.2026.8.26.0561</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
-        </is>
-      </c>
-      <c r="C12" s="21">
+          <t>Bistrô 42</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="str">
         <f>IF(B12="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B12,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H12" s="32" t="n">
-        <v>11300</v>
+        <v>9500</v>
       </c>
       <c r="I12" s="32" t="n">
-        <v>11300</v>
+        <v>5300</v>
       </c>
       <c r="J12" s="22">
         <f>IF(B12="","",H12-I12)</f>
-        <v/>
+        <v>4200</v>
       </c>
       <c r="K12" s="33" t="n">
-        <v>45746</v>
-      </c>
-      <c r="L12" s="21">
+        <v>46034</v>
+      </c>
+      <c r="L12" s="21" t="str">
         <f>IF(B12="","",IF(E12=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M12" s="23">
         <f>IF(OR(B12="",H12=0,H12=""),"",I12/H12)</f>
-        <v/>
+        <v>0.557894736842105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>4352718-43.2025.8.26.0498</t>
+          <t>9236009-85.2025.8.26.0452</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
-        </is>
-      </c>
-      <c r="C13" s="21">
+          <t>Bistrô 42</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="str">
         <f>IF(B13="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B13,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D13" s="29" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E13" s="29" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Execução</t>
         </is>
       </c>
       <c r="F13" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="H13" s="32" t="n">
-        <v>9300</v>
+        <v>4000</v>
       </c>
       <c r="I13" s="32" t="n">
-        <v>4650</v>
+        <v>0</v>
       </c>
       <c r="J13" s="22">
         <f>IF(B13="","",H13-I13)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="K13" s="33" t="n">
-        <v>45790</v>
-      </c>
-      <c r="L13" s="21">
+        <v>45887</v>
+      </c>
+      <c r="L13" s="21" t="str">
         <f>IF(B13="","",IF(E13=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M13" s="23">
         <f>IF(OR(B13="",H13=0,H13=""),"",I13/H13)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>2650441-66.2026.8.26.0528</t>
+          <t>5025425-10.2025.8.26.0629</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
-        </is>
-      </c>
-      <c r="C14" s="21">
+          <t>Roberto Almeida</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="str">
         <f>IF(B14="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B14,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D14" s="29" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="E14" s="29" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="F14" s="29" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="G14" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H14" s="32" t="n">
-        <v>7800</v>
+        <v>15000</v>
       </c>
       <c r="I14" s="32" t="n">
-        <v>7800</v>
+        <v>15000</v>
       </c>
       <c r="J14" s="22">
         <f>IF(B14="","",H14-I14)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K14" s="33" t="n">
-        <v>46225</v>
-      </c>
-      <c r="L14" s="21">
+        <v>45992</v>
+      </c>
+      <c r="L14" s="21" t="str">
         <f>IF(B14="","",IF(E14=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M14" s="23">
         <f>IF(OR(B14="",H14=0,H14=""),"",I14/H14)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>5470559-73.2026.8.26.0380</t>
+          <t>2354318-24.2026.8.26.0295</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
-        </is>
-      </c>
-      <c r="C15" s="21">
+          <t>Roberto Almeida</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="str">
         <f>IF(B15="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B15,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D15" s="29" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="E15" s="29" t="inlineStr">
@@ -6094,7 +6101,7 @@
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="G15" s="29" t="inlineStr">
@@ -6106,47 +6113,47 @@
         <v>10200</v>
       </c>
       <c r="I15" s="32" t="n">
-        <v>6120</v>
+        <v>7200</v>
       </c>
       <c r="J15" s="22">
         <f>IF(B15="","",H15-I15)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K15" s="33" t="n">
-        <v>46072</v>
-      </c>
-      <c r="L15" s="21">
+        <v>46146</v>
+      </c>
+      <c r="L15" s="21" t="str">
         <f>IF(B15="","",IF(E15=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M15" s="23">
         <f>IF(OR(B15="",H15=0,H15=""),"",I15/H15)</f>
-        <v/>
+        <v>0.705882352941177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>8570388-84.2025.8.26.0560</t>
+          <t>CONS-2025-05</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
-        </is>
-      </c>
-      <c r="C16" s="21">
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="str">
         <f>IF(B16="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B16,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D16" s="29" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="E16" s="29" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F16" s="29" t="inlineStr">
@@ -6160,45 +6167,45 @@
         </is>
       </c>
       <c r="H16" s="32" t="n">
-        <v>10400</v>
+        <v>21600</v>
       </c>
       <c r="I16" s="32" t="n">
-        <v>0</v>
+        <v>19260</v>
       </c>
       <c r="J16" s="22">
         <f>IF(B16="","",H16-I16)</f>
-        <v/>
+        <v>2340</v>
       </c>
       <c r="K16" s="33" t="n">
-        <v>45838</v>
-      </c>
-      <c r="L16" s="21">
+        <v>45971</v>
+      </c>
+      <c r="L16" s="21" t="str">
         <f>IF(B16="","",IF(E16=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M16" s="23">
         <f>IF(OR(B16="",H16=0,H16=""),"",I16/H16)</f>
-        <v/>
+        <v>0.891666666666667</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>6258696-95.2026.8.26.0598</t>
+          <t>2645033-67.2026.8.26.0012</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
-        </is>
-      </c>
-      <c r="C17" s="21">
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="str">
         <f>IF(B17="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B17,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
@@ -6213,54 +6220,54 @@
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H17" s="32" t="n">
-        <v>8000</v>
+        <v>18000</v>
       </c>
       <c r="I17" s="32" t="n">
-        <v>4000</v>
+        <v>15300</v>
       </c>
       <c r="J17" s="22">
         <f>IF(B17="","",H17-I17)</f>
-        <v/>
+        <v>2700</v>
       </c>
       <c r="K17" s="33" t="n">
-        <v>46214</v>
-      </c>
-      <c r="L17" s="21">
+        <v>46160</v>
+      </c>
+      <c r="L17" s="21" t="str">
         <f>IF(B17="","",IF(E17=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M17" s="23">
         <f>IF(OR(B17="",H17=0,H17=""),"",I17/H17)</f>
-        <v/>
+        <v>0.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>9467819-47.2025.8.26.0087</t>
+          <t>9225646-96.2025.8.26.0322</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>José Antônio Ribeiro</t>
-        </is>
-      </c>
-      <c r="C18" s="21">
+          <t>Transportadora Rota Sul</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="str">
         <f>IF(B18="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B18,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
@@ -6270,45 +6277,45 @@
       </c>
       <c r="G18" s="29" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H18" s="32" t="n">
-        <v>6200</v>
+        <v>13500</v>
       </c>
       <c r="I18" s="32" t="n">
-        <v>6200</v>
+        <v>13500</v>
       </c>
       <c r="J18" s="22">
         <f>IF(B18="","",H18-I18)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K18" s="33" t="n">
-        <v>45775</v>
-      </c>
-      <c r="L18" s="21">
+        <v>45992</v>
+      </c>
+      <c r="L18" s="21" t="str">
         <f>IF(B18="","",IF(E18=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M18" s="23">
         <f>IF(OR(B18="",H18=0,H18=""),"",I18/H18)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>4300029-58.2025.8.26.0015</t>
+          <t>4526984-60.2026.8.26.0258</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="C19" s="21">
+          <t>Transportadora Rota Sul</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="str">
         <f>IF(B19="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B19,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
@@ -6317,7 +6324,7 @@
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
@@ -6327,111 +6334,111 @@
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="H19" s="32" t="n">
-        <v>10300</v>
+        <v>9000</v>
       </c>
       <c r="I19" s="32" t="n">
-        <v>10300</v>
+        <v>0</v>
       </c>
       <c r="J19" s="22">
         <f>IF(B19="","",H19-I19)</f>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="K19" s="33" t="n">
-        <v>45946</v>
-      </c>
-      <c r="L19" s="21">
+        <v>46125</v>
+      </c>
+      <c r="L19" s="21" t="str">
         <f>IF(B19="","",IF(E19=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M19" s="23">
         <f>IF(OR(B19="",H19=0,H19=""),"",I19/H19)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>8986364-51.2026.8.26.0700</t>
+          <t>CONS-2026-06</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
-        </is>
-      </c>
-      <c r="C20" s="21">
+          <t>Transportadora Rota Sul</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="str">
         <f>IF(B20="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B20,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G20" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H20" s="32" t="n">
-        <v>14900</v>
+        <v>4400</v>
       </c>
       <c r="I20" s="32" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="J20" s="22">
         <f>IF(B20="","",H20-I20)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K20" s="33" t="n">
-        <v>46207</v>
-      </c>
-      <c r="L20" s="21">
+        <v>46216</v>
+      </c>
+      <c r="L20" s="21" t="str">
         <f>IF(B20="","",IF(E20=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M20" s="23">
         <f>IF(OR(B20="",H20=0,H20=""),"",I20/H20)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>9717671-36.2026.8.26.0445</t>
+          <t>6832730-55.2026.8.26.0386</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="C21" s="21">
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="str">
         <f>IF(B21="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B21,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Acordo</t>
         </is>
       </c>
       <c r="F21" s="29" t="inlineStr">
@@ -6441,49 +6448,49 @@
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H21" s="32" t="n">
-        <v>11800</v>
+        <v>9000</v>
       </c>
       <c r="I21" s="32" t="n">
-        <v>11800</v>
+        <v>9000</v>
       </c>
       <c r="J21" s="22">
         <f>IF(B21="","",H21-I21)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K21" s="33" t="n">
-        <v>46135</v>
-      </c>
-      <c r="L21" s="21">
+        <v>46097</v>
+      </c>
+      <c r="L21" s="21" t="str">
         <f>IF(B21="","",IF(E21=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M21" s="23">
         <f>IF(OR(B21="",H21=0,H21=""),"",I21/H21)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>1808451-67.2026.8.26.0657</t>
+          <t>9616569-91.2026.8.26.0079</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
-        </is>
-      </c>
-      <c r="C22" s="21">
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="str">
         <f>IF(B22="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B22,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D22" s="29" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="E22" s="29" t="inlineStr">
@@ -6493,116 +6500,116 @@
       </c>
       <c r="F22" s="29" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H22" s="32" t="n">
-        <v>7900</v>
+        <v>6600</v>
       </c>
       <c r="I22" s="32" t="n">
-        <v>2370</v>
+        <v>4500</v>
       </c>
       <c r="J22" s="22">
         <f>IF(B22="","",H22-I22)</f>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="K22" s="33" t="n">
-        <v>46188</v>
-      </c>
-      <c r="L22" s="21">
+        <v>46181</v>
+      </c>
+      <c r="L22" s="21" t="str">
         <f>IF(B22="","",IF(E22=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M22" s="23">
         <f>IF(OR(B22="",H22=0,H22=""),"",I22/H22)</f>
-        <v/>
+        <v>0.681818181818182</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>3310587-30.2026.8.26.0678</t>
+          <t>6710873-21.2025.8.26.0571</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
-        </is>
-      </c>
-      <c r="C23" s="21">
+          <t>Escola Aurora</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="str">
         <f>IF(B23="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B23,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="E23" s="29" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="H23" s="32" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="I23" s="32" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="J23" s="22">
         <f>IF(B23="","",H23-I23)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="K23" s="33" t="n">
-        <v>46036</v>
-      </c>
-      <c r="L23" s="21">
+        <v>45950</v>
+      </c>
+      <c r="L23" s="21" t="str">
         <f>IF(B23="","",IF(E23=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M23" s="23">
         <f>IF(OR(B23="",H23=0,H23=""),"",I23/H23)</f>
-        <v/>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>3930894-43.2025.8.26.0476</t>
+          <t>5900991-46.2026.8.26.0469</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Ana Beatriz Moreira</t>
-        </is>
-      </c>
-      <c r="C24" s="21">
+          <t>José Antônio Ribeiro</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="str">
         <f>IF(B24="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B24,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
@@ -6616,98 +6623,98 @@
         </is>
       </c>
       <c r="H24" s="32" t="n">
-        <v>6600</v>
+        <v>4000</v>
       </c>
       <c r="I24" s="32" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="J24" s="22">
         <f>IF(B24="","",H24-I24)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="K24" s="33" t="n">
-        <v>45835</v>
-      </c>
-      <c r="L24" s="21">
+        <v>46048</v>
+      </c>
+      <c r="L24" s="21" t="str">
         <f>IF(B24="","",IF(E24=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M24" s="23">
         <f>IF(OR(B24="",H24=0,H24=""),"",I24/H24)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>9802987-45.2025.8.26.0097</t>
+          <t>3363714-92.2025.8.26.0592</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
-        </is>
-      </c>
-      <c r="C25" s="21">
+          <t>Oficina Mecânica Central</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="str">
         <f>IF(B25="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B25,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D25" s="29" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E25" s="29" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G25" s="29" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H25" s="32" t="n">
-        <v>13900</v>
+        <v>15000</v>
       </c>
       <c r="I25" s="32" t="n">
-        <v>13900</v>
+        <v>15000</v>
       </c>
       <c r="J25" s="22">
         <f>IF(B25="","",H25-I25)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K25" s="33" t="n">
-        <v>45926</v>
-      </c>
-      <c r="L25" s="21">
+        <v>45978</v>
+      </c>
+      <c r="L25" s="21" t="str">
         <f>IF(B25="","",IF(E25=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M25" s="23">
         <f>IF(OR(B25="",H25=0,H25=""),"",I25/H25)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>6904743-30.2025.8.26.0361</t>
+          <t>6184138-13.2026.8.26.0378</t>
         </is>
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Nunes</t>
-        </is>
-      </c>
-      <c r="C26" s="21">
+          <t>Oficina Mecânica Central</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="str">
         <f>IF(B26="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B26,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
@@ -6716,7 +6723,7 @@
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
@@ -6726,54 +6733,54 @@
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="H26" s="32" t="n">
-        <v>10400</v>
+        <v>9000</v>
       </c>
       <c r="I26" s="32" t="n">
-        <v>10400</v>
+        <v>4500</v>
       </c>
       <c r="J26" s="22">
         <f>IF(B26="","",H26-I26)</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="K26" s="33" t="n">
-        <v>45794</v>
-      </c>
-      <c r="L26" s="21">
+        <v>46125</v>
+      </c>
+      <c r="L26" s="21" t="str">
         <f>IF(B26="","",IF(E26=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M26" s="23">
         <f>IF(OR(B26="",H26=0,H26=""),"",I26/H26)</f>
-        <v/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>5497983-95.2025.8.26.0570</t>
+          <t>7099226-69.2026.8.26.0433</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Loja Verde Comércio</t>
-        </is>
-      </c>
-      <c r="C27" s="21">
+          <t>Luciana Farias</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="str">
         <f>IF(B27="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B27,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F27" s="29" t="inlineStr">
@@ -6787,107 +6794,107 @@
         </is>
       </c>
       <c r="H27" s="32" t="n">
-        <v>9400</v>
+        <v>12000</v>
       </c>
       <c r="I27" s="32" t="n">
-        <v>2820</v>
+        <v>12000</v>
       </c>
       <c r="J27" s="22">
         <f>IF(B27="","",H27-I27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K27" s="33" t="n">
-        <v>45972</v>
-      </c>
-      <c r="L27" s="21">
+        <v>46167</v>
+      </c>
+      <c r="L27" s="21" t="str">
         <f>IF(B27="","",IF(E27=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M27" s="23">
         <f>IF(OR(B27="",H27=0,H27=""),"",I27/H27)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>4112092-92.2025.8.26.0646</t>
+          <t>2521428-61.2026.8.26.0600</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
-        </is>
-      </c>
-      <c r="C28" s="21">
+          <t>Luciana Farias</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="str">
         <f>IF(B28="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B28,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Acordo</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="H28" s="32" t="n">
-        <v>4200</v>
+        <v>7600</v>
       </c>
       <c r="I28" s="32" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="J28" s="22">
         <f>IF(B28="","",H28-I28)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="K28" s="33" t="n">
-        <v>45813</v>
-      </c>
-      <c r="L28" s="21">
+        <v>46202</v>
+      </c>
+      <c r="L28" s="21" t="str">
         <f>IF(B28="","",IF(E28=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M28" s="23">
         <f>IF(OR(B28="",H28=0,H28=""),"",I28/H28)</f>
-        <v/>
+        <v>0.473684210526316</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>5297049-18.2026.8.26.0015</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
-        </is>
-      </c>
-      <c r="C29" s="21">
+          <t>Agência Prisma</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="str">
         <f>IF(B29="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B29,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>Execução</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
@@ -6897,45 +6904,45 @@
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Hora</t>
         </is>
       </c>
       <c r="H29" s="32" t="n">
-        <v>11700</v>
+        <v>24000</v>
       </c>
       <c r="I29" s="32" t="n">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="J29" s="22">
         <f>IF(B29="","",H29-I29)</f>
-        <v/>
+        <v>5100</v>
       </c>
       <c r="K29" s="33" t="n">
-        <v>46194</v>
-      </c>
-      <c r="L29" s="21">
+        <v>45999</v>
+      </c>
+      <c r="L29" s="21" t="str">
         <f>IF(B29="","",IF(E29=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M29" s="23">
         <f>IF(OR(B29="",H29=0,H29=""),"",I29/H29)</f>
-        <v/>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>6877173-50.2026.8.26.0467</t>
+          <t>CONS-2026-07</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
-        </is>
-      </c>
-      <c r="C30" s="21">
+          <t>Agência Prisma</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="str">
         <f>IF(B30="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B30,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
@@ -6944,7 +6951,7 @@
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
@@ -6954,159 +6961,159 @@
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H30" s="32" t="n">
-        <v>21100</v>
+        <v>7000</v>
       </c>
       <c r="I30" s="32" t="n">
-        <v>10550</v>
+        <v>7000</v>
       </c>
       <c r="J30" s="22">
         <f>IF(B30="","",H30-I30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K30" s="33" t="n">
-        <v>46201</v>
-      </c>
-      <c r="L30" s="21">
+        <v>46118</v>
+      </c>
+      <c r="L30" s="21" t="str">
         <f>IF(B30="","",IF(E30=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M30" s="23">
         <f>IF(OR(B30="",H30=0,H30=""),"",I30/H30)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="27" t="inlineStr">
         <is>
-          <t>3003874-97.2026.8.26.0384</t>
+          <t>9495290-86.2025.8.26.0503</t>
         </is>
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
-        </is>
-      </c>
-      <c r="C31" s="21">
+          <t>Helena Duarte</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="str">
         <f>IF(B31="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B31,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Execução</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="H31" s="32" t="n">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="I31" s="32" t="n">
-        <v>4080</v>
+        <v>0</v>
       </c>
       <c r="J31" s="22">
         <f>IF(B31="","",H31-I31)</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="K31" s="33" t="n">
-        <v>46039</v>
-      </c>
-      <c r="L31" s="21">
+        <v>45852</v>
+      </c>
+      <c r="L31" s="21" t="str">
         <f>IF(B31="","",IF(E31=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M31" s="23">
         <f>IF(OR(B31="",H31=0,H31=""),"",I31/H31)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>6545676-47.2025.8.26.0126</t>
+          <t>7679821-77.2026.8.26.0265</t>
         </is>
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
-        </is>
-      </c>
-      <c r="C32" s="21">
+          <t>Helena Duarte</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="str">
         <f>IF(B32="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B32,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H32" s="32" t="n">
-        <v>6600</v>
+        <v>7500</v>
       </c>
       <c r="I32" s="32" t="n">
-        <v>3960</v>
+        <v>4500</v>
       </c>
       <c r="J32" s="22">
         <f>IF(B32="","",H32-I32)</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="K32" s="33" t="n">
-        <v>45895</v>
-      </c>
-      <c r="L32" s="21">
+        <v>46195</v>
+      </c>
+      <c r="L32" s="21" t="str">
         <f>IF(B32="","",IF(E32=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M32" s="23">
         <f>IF(OR(B32="",H32=0,H32=""),"",I32/H32)</f>
-        <v/>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="27" t="inlineStr">
         <is>
-          <t>1941959-24.2026.8.26.0167</t>
+          <t>8045862-82.2026.8.26.0491</t>
         </is>
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
-        </is>
-      </c>
-      <c r="C33" s="21">
+          <t>Carlos Eduardo Nunes</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="str">
         <f>IF(B33="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B33,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
@@ -7115,7 +7122,7 @@
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
@@ -7125,59 +7132,59 @@
       </c>
       <c r="G33" s="29" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="H33" s="32" t="n">
-        <v>6500</v>
+        <v>7600</v>
       </c>
       <c r="I33" s="32" t="n">
-        <v>6500</v>
+        <v>3600</v>
       </c>
       <c r="J33" s="22">
         <f>IF(B33="","",H33-I33)</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="K33" s="33" t="n">
-        <v>46239</v>
-      </c>
-      <c r="L33" s="21">
+        <v>46090</v>
+      </c>
+      <c r="L33" s="21" t="str">
         <f>IF(B33="","",IF(E33=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M33" s="23">
         <f>IF(OR(B33="",H33=0,H33=""),"",I33/H33)</f>
-        <v/>
+        <v>0.473684210526316</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>3118925-55.2025.8.26.0426</t>
+          <t>9605863-76.2026.8.26.0026</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
-        </is>
-      </c>
-      <c r="C34" s="21">
+          <t>Marcos Vinícius Teles</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="str">
         <f>IF(B34="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B34,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
@@ -7186,41 +7193,41 @@
         </is>
       </c>
       <c r="H34" s="32" t="n">
-        <v>4500</v>
+        <v>5400</v>
       </c>
       <c r="I34" s="32" t="n">
-        <v>2250</v>
+        <v>5400</v>
       </c>
       <c r="J34" s="22">
         <f>IF(B34="","",H34-I34)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K34" s="33" t="n">
-        <v>45897</v>
-      </c>
-      <c r="L34" s="21">
+        <v>46174</v>
+      </c>
+      <c r="L34" s="21" t="str">
         <f>IF(B34="","",IF(E34=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="M34" s="23">
         <f>IF(OR(B34="",H34=0,H34=""),"",I34/H34)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="27" t="inlineStr">
         <is>
-          <t>7658179-42.2026.8.26.0152</t>
+          <t>4766902-26.2025.8.26.0051</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
-        </is>
-      </c>
-      <c r="C35" s="21">
+          <t>Padaria do Sol Ltda</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="str">
         <f>IF(B35="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B35,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
@@ -7229,7 +7236,7 @@
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
@@ -7239,159 +7246,159 @@
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H35" s="32" t="n">
-        <v>18300</v>
+        <v>12000</v>
       </c>
       <c r="I35" s="32" t="n">
-        <v>18300</v>
+        <v>12000</v>
       </c>
       <c r="J35" s="22">
         <f>IF(B35="","",H35-I35)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K35" s="33" t="n">
-        <v>46035</v>
-      </c>
-      <c r="L35" s="21">
+        <v>45964</v>
+      </c>
+      <c r="L35" s="21" t="str">
         <f>IF(B35="","",IF(E35=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="M35" s="23">
         <f>IF(OR(B35="",H35=0,H35=""),"",I35/H35)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>3326285-90.2025.8.26.0608</t>
+          <t>9778116-95.2025.8.26.0106</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>José Antônio Ribeiro</t>
-        </is>
-      </c>
-      <c r="C36" s="21">
+          <t>Construtora Horizonte</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="str">
         <f>IF(B36="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B36,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="H36" s="32" t="n">
-        <v>5500</v>
+        <v>18000</v>
       </c>
       <c r="I36" s="32" t="n">
-        <v>2750</v>
+        <v>18000</v>
       </c>
       <c r="J36" s="22">
         <f>IF(B36="","",H36-I36)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K36" s="33" t="n">
-        <v>45769</v>
-      </c>
-      <c r="L36" s="21">
+        <v>45810</v>
+      </c>
+      <c r="L36" s="21" t="str">
         <f>IF(B36="","",IF(E36=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="M36" s="23">
         <f>IF(OR(B36="",H36=0,H36=""),"",I36/H36)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="27" t="inlineStr">
         <is>
-          <t>1191416-90.2025.8.26.0249</t>
+          <t>8204296-70.2025.8.26.0146</t>
         </is>
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
-        </is>
-      </c>
-      <c r="C37" s="21">
+          <t>Marcos Vinícius Teles</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="str">
         <f>IF(B37="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B37,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Instrução</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="H37" s="32" t="n">
-        <v>12400</v>
+        <v>6500</v>
       </c>
       <c r="I37" s="32" t="n">
-        <v>6200</v>
+        <v>6500</v>
       </c>
       <c r="J37" s="22">
         <f>IF(B37="","",H37-I37)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K37" s="33" t="n">
-        <v>45988</v>
-      </c>
-      <c r="L37" s="21">
+        <v>45702</v>
+      </c>
+      <c r="L37" s="21" t="str">
         <f>IF(B37="","",IF(E37=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="M37" s="23">
         <f>IF(OR(B37="",H37=0,H37=""),"",I37/H37)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>5626517-53.2026.8.26.0206</t>
+          <t>9088515-39.2025.8.26.0125</t>
         </is>
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
-        </is>
-      </c>
-      <c r="C38" s="21">
+          <t>Loja Verde Comércio</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="str">
         <f>IF(B38="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B38,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
@@ -7400,7 +7407,7 @@
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
@@ -7410,49 +7417,49 @@
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H38" s="32" t="n">
-        <v>16900</v>
+        <v>6000</v>
       </c>
       <c r="I38" s="32" t="n">
-        <v>5070</v>
+        <v>6000</v>
       </c>
       <c r="J38" s="22">
         <f>IF(B38="","",H38-I38)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K38" s="33" t="n">
-        <v>46105</v>
-      </c>
-      <c r="L38" s="21">
+        <v>45915</v>
+      </c>
+      <c r="L38" s="21" t="str">
         <f>IF(B38="","",IF(E38=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="M38" s="23">
         <f>IF(OR(B38="",H38=0,H38=""),"",I38/H38)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="27" t="inlineStr">
         <is>
-          <t>6237740-34.2025.8.26.0163</t>
+          <t>8663770-96.2025.8.26.0481</t>
         </is>
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
-        </is>
-      </c>
-      <c r="C39" s="21">
+          <t>Oficina Mecânica Central</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="str">
         <f>IF(B39="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B39,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PJ</v>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
@@ -7467,49 +7474,49 @@
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H39" s="32" t="n">
-        <v>5700</v>
+        <v>12000</v>
       </c>
       <c r="I39" s="32" t="n">
-        <v>5700</v>
+        <v>12000</v>
       </c>
       <c r="J39" s="22">
         <f>IF(B39="","",H39-I39)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K39" s="33" t="n">
-        <v>45791</v>
-      </c>
-      <c r="L39" s="21">
+        <v>45782</v>
+      </c>
+      <c r="L39" s="21" t="str">
         <f>IF(B39="","",IF(E39=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="M39" s="23">
         <f>IF(OR(B39="",H39=0,H39=""),"",I39/H39)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="27" t="inlineStr">
         <is>
-          <t>9778303-99.2026.8.26.0419</t>
+          <t>5211189-81.2025.8.26.0412</t>
         </is>
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
-        </is>
-      </c>
-      <c r="C40" s="21">
+          <t>Fernanda Castro</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="str">
         <f>IF(B40="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B40,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
@@ -7524,49 +7531,49 @@
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="H40" s="32" t="n">
-        <v>14100</v>
+        <v>7000</v>
       </c>
       <c r="I40" s="32" t="n">
-        <v>14100</v>
+        <v>7000</v>
       </c>
       <c r="J40" s="22">
         <f>IF(B40="","",H40-I40)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K40" s="33" t="n">
-        <v>46254</v>
-      </c>
-      <c r="L40" s="21">
+        <v>45936</v>
+      </c>
+      <c r="L40" s="21" t="str">
         <f>IF(B40="","",IF(E40=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="M40" s="23">
         <f>IF(OR(B40="",H40=0,H40=""),"",I40/H40)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="27" t="inlineStr">
         <is>
-          <t>3314594-22.2025.8.26.0019</t>
+          <t>6161129-80.2025.8.26.0663</t>
         </is>
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
-        </is>
-      </c>
-      <c r="C41" s="21">
+          <t>José Antônio Ribeiro</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="str">
         <f>IF(B41="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B41,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
@@ -7576,40 +7583,40 @@
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="H41" s="32" t="n">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="I41" s="32" t="n">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="J41" s="22">
         <f>IF(B41="","",H41-I41)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K41" s="33" t="n">
-        <v>45878</v>
-      </c>
-      <c r="L41" s="21">
+        <v>45748</v>
+      </c>
+      <c r="L41" s="21" t="str">
         <f>IF(B41="","",IF(E41=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="M41" s="23">
         <f>IF(OR(B41="",H41=0,H41=""),"",I41/H41)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="27" t="inlineStr">
         <is>
-          <t>7598076-58.2025.8.26.0552</t>
+          <t>9420478-99.2025.8.26.0491</t>
         </is>
       </c>
       <c r="B42" s="27" t="inlineStr">
@@ -7617,13 +7624,13 @@
           <t>Ana Beatriz Moreira</t>
         </is>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="21" t="str">
         <f>IF(B42="","",IFERROR(INDEX(Clientes!$B$5:$B$64,MATCH(B42,Clientes!$A$5:$A$64,0)),""))</f>
-        <v/>
+        <v>PF</v>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
@@ -7633,34 +7640,34 @@
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="H42" s="32" t="n">
-        <v>11300</v>
+        <v>8500</v>
       </c>
       <c r="I42" s="32" t="n">
-        <v>11300</v>
+        <v>8500</v>
       </c>
       <c r="J42" s="22">
         <f>IF(B42="","",H42-I42)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K42" s="33" t="n">
-        <v>45945</v>
-      </c>
-      <c r="L42" s="21">
+        <v>45677</v>
+      </c>
+      <c r="L42" s="21" t="str">
         <f>IF(B42="","",IF(E42=Config!$B$6,"Encerrado","Ativo"))</f>
-        <v/>
+        <v>Encerrado</v>
       </c>
       <c r="M42" s="23">
         <f>IF(OR(B42="",H42=0,H42=""),"",I42/H42)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -12040,7 +12047,7 @@
     <row r="206">
       <c r="A206" s="25" t="inlineStr">
         <is>
-          <t>Recebido em vermelho: está maior que o valor contratado; confira o contrato ou o valor lançado. Linhas cinza: casos encerrados.</t>
+          <t>Recebido em vermelho: está maior que o valor contratado; confira o contrato ou o valor lançado. Linhas cinza: casos encerrados. Recebido = soma das parcelas pagas do caso na planilha 14 (2025 e 2026); em misto, o contratado inclui o êxito esperado.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
@@ -23,9 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -204,13 +205,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,7 +228,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -239,21 +240,21 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -792,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -953,17 +954,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2643,9 +2656,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="28">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="28" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="6">
@@ -5391,7 +5403,7 @@
     <dataValidation sqref="B5:B64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"PF,PJ"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$9,0,0,MAX(1,COUNTA(Config!$A$9:$A$18)),1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -12069,7 +12081,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="B5:B204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:B204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Clientes!$A$5,0,0,MAX(1,COUNTA(Clientes!$A$5:$A$64)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -12084,10 +12096,10 @@
     <dataValidation sqref="G5:G204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$G$9,0,0,MAX(1,COUNTA(Config!$G$9:$G$18)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="H5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/13-carteira-de-clientes-e-casos.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
